--- a/out/thesis/models/regression_coefficients.xlsx
+++ b/out/thesis/models/regression_coefficients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="25">
   <si>
     <t>model</t>
   </si>
@@ -89,21 +89,6 @@
   </si>
   <si>
     <t>CLOSE_VOLATILITY_60D</t>
-  </si>
-  <si>
-    <t>CLOSE_ROE</t>
-  </si>
-  <si>
-    <t>CLOSE_P_B</t>
-  </si>
-  <si>
-    <t>CLOSE_P_E</t>
-  </si>
-  <si>
-    <t>CLOSE_TOTAL_ASSETS</t>
-  </si>
-  <si>
-    <t>CLOSE_MARKET_CAP</t>
   </si>
 </sst>
 </file>
@@ -435,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -764,28 +749,28 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>-0.01620064028776349</v>
+        <v>-0.01045809208898529</v>
       </c>
       <c r="E10">
-        <v>0.01836137637501679</v>
+        <v>0.02121450967635894</v>
       </c>
       <c r="F10">
-        <v>-0.8823216711469798</v>
+        <v>-0.4929688335262159</v>
       </c>
       <c r="G10">
-        <v>0.3776028804702731</v>
+        <v>0.6220346091830855</v>
       </c>
       <c r="H10">
-        <v>-0.05218827668938102</v>
+        <v>-0.0520377670043253</v>
       </c>
       <c r="I10">
-        <v>0.01978699611385403</v>
+        <v>0.03112158282635472</v>
       </c>
       <c r="J10">
         <v>52</v>
       </c>
       <c r="K10">
-        <v>0.1629842427406559</v>
+        <v>-0.03160606734125149</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -799,28 +784,28 @@
         <v>16</v>
       </c>
       <c r="D11">
-        <v>-0.02363874751029485</v>
+        <v>-0.01602652568202886</v>
       </c>
       <c r="E11">
-        <v>0.03045389621774993</v>
+        <v>0.02441352600574445</v>
       </c>
       <c r="F11">
-        <v>-0.7762142269506094</v>
+        <v>-0.6564609175363629</v>
       </c>
       <c r="G11">
-        <v>0.4376225072197697</v>
+        <v>0.5115276060248322</v>
       </c>
       <c r="H11">
-        <v>-0.08332728728600527</v>
+        <v>-0.06387615738892</v>
       </c>
       <c r="I11">
-        <v>0.03604979226541558</v>
+        <v>0.03182310602486227</v>
       </c>
       <c r="J11">
         <v>52</v>
       </c>
       <c r="K11">
-        <v>0.1629842427406559</v>
+        <v>-0.03160606734125149</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -831,31 +816,31 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12">
-        <v>0.009589303076724988</v>
+        <v>0.04165368440259408</v>
       </c>
       <c r="E12">
-        <v>0.01756506973315275</v>
+        <v>0.009916336930342287</v>
       </c>
       <c r="F12">
-        <v>0.5459302594527078</v>
+        <v>4.200511206425526</v>
       </c>
       <c r="G12">
-        <v>0.5851138772734283</v>
+        <v>2.663129853378493E-05</v>
       </c>
       <c r="H12">
-        <v>-0.02483760098618899</v>
+        <v>0.02221802116055872</v>
       </c>
       <c r="I12">
-        <v>0.04401620713963896</v>
+        <v>0.06108934764462944</v>
       </c>
       <c r="J12">
         <v>52</v>
       </c>
       <c r="K12">
-        <v>0.1629842427406559</v>
+        <v>-0.03160606734125149</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -869,28 +854,28 @@
         <v>23</v>
       </c>
       <c r="D13">
-        <v>-0.0008622403689781297</v>
+        <v>0.0008269515535928361</v>
       </c>
       <c r="E13">
-        <v>0.0007295313252131076</v>
+        <v>0.000960146271018933</v>
       </c>
       <c r="F13">
-        <v>-1.181910000542137</v>
+        <v>0.8612766393554316</v>
       </c>
       <c r="G13">
-        <v>0.2372414134551485</v>
+        <v>0.3890856986666523</v>
       </c>
       <c r="H13">
-        <v>-0.002292095491989598</v>
+        <v>-0.001054900557494707</v>
       </c>
       <c r="I13">
-        <v>0.0005676147540333385</v>
+        <v>0.002708803664680379</v>
       </c>
       <c r="J13">
         <v>52</v>
       </c>
       <c r="K13">
-        <v>0.1629842427406559</v>
+        <v>-0.03160606734125149</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -904,28 +889,28 @@
         <v>24</v>
       </c>
       <c r="D14">
-        <v>-0.0003317004568037969</v>
+        <v>-0.01390825988619754</v>
       </c>
       <c r="E14">
-        <v>0.02302730276376155</v>
+        <v>0.07484822479535926</v>
       </c>
       <c r="F14">
-        <v>-0.0144046595559511</v>
+        <v>-0.185819502389319</v>
       </c>
       <c r="G14">
-        <v>0.9885071419883218</v>
+        <v>0.8525863101900851</v>
       </c>
       <c r="H14">
-        <v>-0.04546438453487608</v>
+        <v>-0.1606080847918595</v>
       </c>
       <c r="I14">
-        <v>0.04480098362126848</v>
+        <v>0.1327915650194645</v>
       </c>
       <c r="J14">
         <v>52</v>
       </c>
       <c r="K14">
-        <v>0.1629842427406559</v>
+        <v>-0.03160606734125149</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -939,28 +924,28 @@
         <v>21</v>
       </c>
       <c r="D15">
-        <v>5.624017493289861E-05</v>
+        <v>0.0001351249119815998</v>
       </c>
       <c r="E15">
-        <v>0.0001080807866519651</v>
+        <v>0.0001523117519124321</v>
       </c>
       <c r="F15">
-        <v>0.520353123575975</v>
+        <v>0.8871601191960981</v>
       </c>
       <c r="G15">
-        <v>0.6028174758500224</v>
+        <v>0.3749927003567602</v>
       </c>
       <c r="H15">
-        <v>-0.0001555942743257105</v>
+        <v>-0.0001634006361889669</v>
       </c>
       <c r="I15">
-        <v>0.0002680746241915077</v>
+        <v>0.0004336504601521665</v>
       </c>
       <c r="J15">
         <v>52</v>
       </c>
       <c r="K15">
-        <v>0.1629842427406559</v>
+        <v>-0.03160606734125149</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -971,171 +956,31 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D16">
-        <v>0.0007299983317370362</v>
+        <v>-5.768588534874254E-06</v>
       </c>
       <c r="E16">
-        <v>0.0004413702285761481</v>
+        <v>6.4612106977064E-06</v>
       </c>
       <c r="F16">
-        <v>1.653936501544286</v>
+        <v>-0.8928030371957979</v>
       </c>
       <c r="G16">
-        <v>0.09814041517565886</v>
+        <v>0.3719626595886223</v>
       </c>
       <c r="H16">
-        <v>-0.0001350714201204255</v>
+        <v>-1.843232879890371E-05</v>
       </c>
       <c r="I16">
-        <v>0.001595068083594498</v>
+        <v>6.895151729155205E-06</v>
       </c>
       <c r="J16">
         <v>52</v>
       </c>
       <c r="K16">
-        <v>0.1629842427406559</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17">
-        <v>-0.005407473788348855</v>
-      </c>
-      <c r="E17">
-        <v>0.002528395163892783</v>
-      </c>
-      <c r="F17">
-        <v>-2.13869804276297</v>
-      </c>
-      <c r="G17">
-        <v>0.03246013124362367</v>
-      </c>
-      <c r="H17">
-        <v>-0.01036303724826396</v>
-      </c>
-      <c r="I17">
-        <v>-0.0004519103284337531</v>
-      </c>
-      <c r="J17">
-        <v>52</v>
-      </c>
-      <c r="K17">
-        <v>0.1629842427406559</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18">
-        <v>0.0007057071915793104</v>
-      </c>
-      <c r="E18">
-        <v>0.000284690716584299</v>
-      </c>
-      <c r="F18">
-        <v>2.478855650954622</v>
-      </c>
-      <c r="G18">
-        <v>0.01318046354680917</v>
-      </c>
-      <c r="H18">
-        <v>0.0001477236403411845</v>
-      </c>
-      <c r="I18">
-        <v>0.001263690742817437</v>
-      </c>
-      <c r="J18">
-        <v>52</v>
-      </c>
-      <c r="K18">
-        <v>0.1629842427406559</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19">
-        <v>-8.565959020972734E-07</v>
-      </c>
-      <c r="E19">
-        <v>4.249555514245279E-07</v>
-      </c>
-      <c r="F19">
-        <v>-2.015730584588927</v>
-      </c>
-      <c r="G19">
-        <v>0.04382815562616398</v>
-      </c>
-      <c r="H19">
-        <v>-1.689493477919707E-06</v>
-      </c>
-      <c r="I19">
-        <v>-2.369832627484001E-08</v>
-      </c>
-      <c r="J19">
-        <v>52</v>
-      </c>
-      <c r="K19">
-        <v>0.1629842427406559</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20">
-        <v>7.752716956607069E-06</v>
-      </c>
-      <c r="E20">
-        <v>3.560400215458756E-06</v>
-      </c>
-      <c r="F20">
-        <v>2.177484689205968</v>
-      </c>
-      <c r="G20">
-        <v>0.02944442295303291</v>
-      </c>
-      <c r="H20">
-        <v>7.744607637592592E-07</v>
-      </c>
-      <c r="I20">
-        <v>1.473097314945488E-05</v>
-      </c>
-      <c r="J20">
-        <v>52</v>
-      </c>
-      <c r="K20">
-        <v>0.1629842427406559</v>
+        <v>-0.03160606734125149</v>
       </c>
     </row>
   </sheetData>
